--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Click any format for the detail.</t>
+          <t>Tap or click any format for the detail.</t>
         </is>
       </c>
     </row>

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20+ pages</t>
+          <t>20 or more pages</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brief &amp; summary</t>
+          <t>Brief and summary</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-4 pages</t>
+          <t>2 to 4 pages</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-40 pages</t>
+          <t>15 to 40 pages</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brief &amp; summary</t>
+          <t>Brief and summary</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-2 pages</t>
+          <t>1 to 2 pages</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brief &amp; summary</t>
+          <t>Brief and summary</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10-25 slides</t>
+          <t>10 to 25 slides</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10-45 minutes</t>
+          <t>10 to 45 minutes</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Digital &amp; interactive</t>
+          <t>Digital and interactive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ongoing / interactive</t>
+          <t>Ongoing and interactive</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Digital &amp; interactive</t>
+          <t>Digital and interactive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-2 pages or a pitch</t>
+          <t>1 to 2 pages or a pitch</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-3 short sections</t>
+          <t>1 to 3 short sections</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5-20 pages</t>
+          <t>5 to 20 pages</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Digital &amp; interactive</t>
+          <t>Digital and interactive</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-20 minutes</t>
+          <t>2 to 20 minutes</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5-15 pages</t>
+          <t>5 to 15 pages</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Half a day to a full day, in person or small-group virtual.</t>
+          <t>Half a day to a full day, in person or small-group virtual</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>45 to 60 minutes, live, often recorded.</t>
+          <t>45 to 60 minutes, live, often recorded</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>One board, roughly 36 by 48 inches.</t>
+          <t>One board, roughly 36 by 48 inches</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Outreach &amp; media</t>
+          <t>Outreach and media</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>600 to 800 words.</t>
+          <t>600 to 800 words</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -2283,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{format} is built for {needed} reach, so reaching {have} means adapting how it is polished and shared.</t>
+          <t>{format} is built {needed}, so {have} means adapting how it is polished and shared.</t>
         </is>
       </c>
     </row>
@@ -2787,6 +2787,66 @@
       <c r="B42" t="inlineStr">
         <is>
           <t>Different objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>reach_built_inside</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>for use inside your court</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>reach_built_outside</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>to reach outside your court</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>reach_use_internal</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>using it inside your court</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>reach_use_external</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>taking it outside your court</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>reach_use_both</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>using it both inside and outside your court</t>
         </is>
       </c>
     </row>
